--- a/data/FBS_SC_Database_v8_1_Clean.xlsx
+++ b/data/FBS_SC_Database_v8_1_Clean.xlsx
@@ -1683,69 +1683,73 @@
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="82" t="inlineStr">
         <is>
           <t>South Carolina</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="82" t="inlineStr">
         <is>
           <t>SEC</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr"/>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>Luke Day</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="C14" s="82" t="inlineStr"/>
+      <c r="D14" s="82" t="inlineStr">
+        <is>
+          <t>Jeff Dillman</t>
+        </is>
+      </c>
+      <c r="E14" s="82" t="inlineStr">
         <is>
           <t>Dir. of Athletic Performance</t>
         </is>
       </c>
-      <c r="F14" s="10" t="n">
+      <c r="F14" s="83" t="n">
         <v>450000</v>
       </c>
-      <c r="G14" s="9" t="n">
+      <c r="G14" s="82" t="n">
         <v>2024</v>
       </c>
-      <c r="H14" s="19" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="I14" s="9" t="inlineStr">
+      <c r="H14" s="84" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="I14" s="82" t="inlineStr">
         <is>
           <t>Mid ($350K-$499K)</t>
         </is>
       </c>
-      <c r="J14" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="M14" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" s="9" t="n">
+      <c r="J14" s="82" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="82" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" s="82" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" s="82" t="n">
         <v>5</v>
       </c>
-      <c r="O14" s="12" t="inlineStr">
+      <c r="O14" s="88" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="P14" s="9" t="inlineStr">
+      <c r="P14" s="82" t="inlineStr">
         <is>
           <t>FootballScoop 2024. Shane Beamer still HC.</t>
         </is>
       </c>
-      <c r="Q14" s="9" t="inlineStr"/>
+      <c r="Q14" s="82" t="inlineStr">
+        <is>
+          <t>[Churn 2026-07-17] Name changed: Luke Day → Jeff Dillman. Salary cleared — requires verification.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="82" t="inlineStr">
@@ -2649,71 +2653,71 @@
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="82" t="inlineStr">
         <is>
           <t>Penn State</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="82" t="inlineStr">
         <is>
           <t>Big Ten</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr"/>
-      <c r="D28" s="65" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="C28" s="82" t="inlineStr"/>
+      <c r="D28" s="85" t="inlineStr">
+        <is>
+          <t>Nittany Lions</t>
+        </is>
+      </c>
+      <c r="E28" s="82" t="inlineStr">
         <is>
           <t>Dir. of S&amp;C</t>
         </is>
       </c>
-      <c r="F28" s="66" t="n">
+      <c r="F28" s="89" t="n">
         <v>350000</v>
       </c>
-      <c r="G28" s="9" t="n">
+      <c r="G28" s="82" t="n">
         <v>2024</v>
       </c>
-      <c r="H28" s="11" t="inlineStr">
-        <is>
-          <t>Estimated</t>
-        </is>
-      </c>
-      <c r="I28" s="9" t="inlineStr">
+      <c r="H28" s="86" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="I28" s="82" t="inlineStr">
         <is>
           <t>Lower Power ($250K-$349K)</t>
         </is>
       </c>
-      <c r="J28" s="9" t="n">
+      <c r="J28" s="82" t="n">
         <v>3</v>
       </c>
-      <c r="K28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="M28" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N28" s="9" t="n">
+      <c r="K28" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="82" t="n">
+        <v>2</v>
+      </c>
+      <c r="M28" s="82" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" s="82" t="n">
         <v>6</v>
       </c>
-      <c r="O28" s="12" t="inlineStr">
+      <c r="O28" s="88" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="P28" s="65" t="inlineStr">
+      <c r="P28" s="85" t="inlineStr">
         <is>
           <t>Franklin fired Oct 12 2025 (3-3 record). Chuck Losey followed Franklin to Virginia Tech. Penn State hired Matt Campbell from Iowa State (Dec 2025). Campbell likely brings new S&amp;C staff. Possibly Reid Kagy (ISU S&amp;C under Campbell) following to PSU — unconfirmed.</t>
         </is>
       </c>
-      <c r="Q28" s="65" t="inlineStr">
-        <is>
-          <t>Franklin fired Oct 2025; Losey to VT; Campbell new HC Dec 2025; new S&amp;C not confirmed.</t>
+      <c r="Q28" s="85" t="inlineStr">
+        <is>
+          <t>[Churn 2026-07-17] Name changed: Unknown → Nittany Lions. Salary cleared — requires verification.</t>
         </is>
       </c>
     </row>
@@ -3822,73 +3826,77 @@
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="14" t="inlineStr">
+      <c r="A45" s="82" t="inlineStr">
         <is>
           <t>Notre Dame</t>
         </is>
       </c>
-      <c r="B45" s="14" t="inlineStr">
+      <c r="B45" s="82" t="inlineStr">
         <is>
           <t>ACC</t>
         </is>
       </c>
-      <c r="C45" s="14" t="inlineStr">
+      <c r="C45" s="82" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D45" s="14" t="inlineStr">
-        <is>
-          <t>Sean Sutton</t>
-        </is>
-      </c>
-      <c r="E45" s="14" t="inlineStr">
+      <c r="D45" s="82" t="inlineStr">
+        <is>
+          <t>Before Notre Dame</t>
+        </is>
+      </c>
+      <c r="E45" s="82" t="inlineStr">
         <is>
           <t>Dir. of Athletic Performance</t>
         </is>
       </c>
-      <c r="F45" s="15" t="n">
+      <c r="F45" s="83" t="n">
         <v>550000</v>
       </c>
-      <c r="G45" s="14" t="n">
+      <c r="G45" s="82" t="n">
         <v>2024</v>
       </c>
-      <c r="H45" s="16" t="inlineStr">
+      <c r="H45" s="86" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="I45" s="82" t="inlineStr">
+        <is>
+          <t>Upper Mid ($500K-$699K)</t>
+        </is>
+      </c>
+      <c r="J45" s="82" t="n">
+        <v>4</v>
+      </c>
+      <c r="K45" s="82" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" s="82" t="n">
+        <v>2</v>
+      </c>
+      <c r="M45" s="82" t="n">
+        <v>2</v>
+      </c>
+      <c r="N45" s="82" t="n">
+        <v>9</v>
+      </c>
+      <c r="O45" s="91" t="inlineStr">
         <is>
           <t>Estimated</t>
         </is>
       </c>
-      <c r="I45" s="14" t="inlineStr">
-        <is>
-          <t>Upper Mid ($500K-$699K)</t>
-        </is>
-      </c>
-      <c r="J45" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="K45" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L45" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="M45" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="N45" s="14" t="n">
-        <v>9</v>
-      </c>
-      <c r="O45" s="17" t="inlineStr">
-        <is>
-          <t>Estimated</t>
-        </is>
-      </c>
-      <c r="P45" s="14" t="inlineStr">
+      <c r="P45" s="82" t="inlineStr">
         <is>
           <t>Private school; est. based on elite program status and CFP regular.</t>
         </is>
       </c>
-      <c r="Q45" s="14" t="inlineStr"/>
+      <c r="Q45" s="82" t="inlineStr">
+        <is>
+          <t>[Churn 2026-07-17] Name changed: Sean Sutton → Before Notre Dame. Salary cleared — requires verification.</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="82" t="inlineStr">
@@ -7982,71 +7990,71 @@
       </c>
     </row>
     <row r="105" ht="16" customHeight="1">
-      <c r="A105" s="14" t="inlineStr">
+      <c r="A105" s="82" t="inlineStr">
         <is>
           <t>Louisiana</t>
         </is>
       </c>
-      <c r="B105" s="14" t="inlineStr">
+      <c r="B105" s="82" t="inlineStr">
         <is>
           <t>Sun Belt</t>
         </is>
       </c>
-      <c r="C105" s="14" t="inlineStr"/>
-      <c r="D105" s="71" t="inlineStr">
-        <is>
-          <t>Connor Neighbors</t>
-        </is>
-      </c>
-      <c r="E105" s="71" t="inlineStr">
+      <c r="C105" s="82" t="inlineStr"/>
+      <c r="D105" s="85" t="inlineStr">
+        <is>
+          <t>Louisiana Football</t>
+        </is>
+      </c>
+      <c r="E105" s="85" t="inlineStr">
         <is>
           <t>Director of Athletic Performance for Football</t>
         </is>
       </c>
-      <c r="F105" s="72" t="n">
+      <c r="F105" s="89" t="n">
         <v>175000</v>
       </c>
-      <c r="G105" s="14" t="n">
+      <c r="G105" s="82" t="n">
         <v>2024</v>
       </c>
-      <c r="H105" s="71" t="inlineStr">
+      <c r="H105" s="85" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="I105" s="82" t="inlineStr">
+        <is>
+          <t>G5 Upper ($175K-$249K)</t>
+        </is>
+      </c>
+      <c r="J105" s="82" t="n">
+        <v>2</v>
+      </c>
+      <c r="K105" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" s="82" t="n">
+        <v>1</v>
+      </c>
+      <c r="M105" s="82" t="n">
+        <v>1</v>
+      </c>
+      <c r="N105" s="82" t="n">
+        <v>4</v>
+      </c>
+      <c r="O105" s="91" t="inlineStr">
         <is>
           <t>Estimated</t>
         </is>
       </c>
-      <c r="I105" s="14" t="inlineStr">
-        <is>
-          <t>G5 Upper ($175K-$249K)</t>
-        </is>
-      </c>
-      <c r="J105" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K105" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M105" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N105" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="O105" s="17" t="inlineStr">
-        <is>
-          <t>Estimated</t>
-        </is>
-      </c>
-      <c r="P105" s="71" t="inlineStr">
+      <c r="P105" s="85" t="inlineStr">
         <is>
           <t>ragincajuns.com staff directory: Neighbors named Dir of Football S&amp;C by HC Desormeaux (announcement via ragincajuns.com). Promoted from within — Asst S&amp;C since 2021. Prior stops: LSU (2016), Alabama. Salary est. Sun Belt upper tier. John Hendrick was incorrect.</t>
         </is>
       </c>
-      <c r="Q105" s="71" t="inlineStr">
-        <is>
-          <t>Name corrected: Connor Neighbors (not John Hendrick). Promoted by HC Desormeaux.</t>
+      <c r="Q105" s="85" t="inlineStr">
+        <is>
+          <t>[Churn 2026-07-17] Name changed: Connor Neighbors → Louisiana Football. Salary cleared — requires verification.</t>
         </is>
       </c>
     </row>
@@ -8396,71 +8404,71 @@
       </c>
     </row>
     <row r="111" ht="16" customHeight="1">
-      <c r="A111" s="14" t="inlineStr">
+      <c r="A111" s="82" t="inlineStr">
         <is>
           <t>Texas State</t>
         </is>
       </c>
-      <c r="B111" s="14" t="inlineStr">
+      <c r="B111" s="82" t="inlineStr">
         <is>
           <t>Sun Belt</t>
         </is>
       </c>
-      <c r="C111" s="14" t="inlineStr"/>
-      <c r="D111" s="71" t="inlineStr">
-        <is>
-          <t>Bret Huth</t>
-        </is>
-      </c>
-      <c r="E111" s="71" t="inlineStr">
+      <c r="C111" s="82" t="inlineStr"/>
+      <c r="D111" s="85" t="inlineStr">
+        <is>
+          <t>Onnit Gym</t>
+        </is>
+      </c>
+      <c r="E111" s="85" t="inlineStr">
         <is>
           <t>Asst AD - S&amp;C / Asst Head Coach Football</t>
         </is>
       </c>
-      <c r="F111" s="72" t="n">
+      <c r="F111" s="89" t="n">
         <v>160000</v>
       </c>
-      <c r="G111" s="14" t="n">
+      <c r="G111" s="82" t="n">
         <v>2024</v>
       </c>
-      <c r="H111" s="71" t="inlineStr">
-        <is>
-          <t>Estimated</t>
-        </is>
-      </c>
-      <c r="I111" s="14" t="inlineStr">
+      <c r="H111" s="85" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="I111" s="82" t="inlineStr">
         <is>
           <t>G5 Mid ($130K-$174K)</t>
         </is>
       </c>
-      <c r="J111" s="71" t="n">
-        <v>2</v>
-      </c>
-      <c r="K111" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="L111" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M111" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N111" s="71" t="n">
+      <c r="J111" s="85" t="n">
+        <v>2</v>
+      </c>
+      <c r="K111" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" s="82" t="n">
+        <v>1</v>
+      </c>
+      <c r="M111" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" s="85" t="n">
         <v>3</v>
       </c>
-      <c r="O111" s="71" t="inlineStr">
+      <c r="O111" s="85" t="inlineStr">
         <is>
           <t>Confirmed (name)</t>
         </is>
       </c>
-      <c r="P111" s="71" t="inlineStr">
+      <c r="P111" s="85" t="inlineStr">
         <is>
           <t>txst.com 2026 live roster: Huth (Asst AD - S&amp;C / Asst HC Football) + Clark Eyers (Assoc S&amp;C Coach) + Drake Hughes (Asst S&amp;C Coach). Huth joined HC GJ Kinne Dec 2022 from UIW (5 yrs); prev Rice, Cal, Memphis, ULM. TX state DB (3/30/2026) shows Andrew Nilo $85K as 'Head Coach S&amp;C' — covers Olympic sports, NOT football. Huth runs the football weight room. NHSSCA TX clinic 2025 confirms Huth presenting on Olympic lifting.</t>
         </is>
       </c>
-      <c r="Q111" s="74" t="inlineStr">
-        <is>
-          <t>CORRECTED: Andrew Nilo (TX DB) = Olympic S&amp;C. Bret Huth confirmed football head S&amp;C per txst.com 2026 live roster.</t>
+      <c r="Q111" s="84" t="inlineStr">
+        <is>
+          <t>[Churn 2026-07-17] Name changed: Bret Huth → Onnit Gym. Salary cleared — requires verification.</t>
         </is>
       </c>
     </row>
@@ -8603,69 +8611,73 @@
       </c>
     </row>
     <row r="114" ht="16" customHeight="1">
-      <c r="A114" s="14" t="inlineStr">
+      <c r="A114" s="82" t="inlineStr">
         <is>
           <t>Ball State</t>
         </is>
       </c>
-      <c r="B114" s="14" t="inlineStr">
+      <c r="B114" s="82" t="inlineStr">
         <is>
           <t>MAC</t>
         </is>
       </c>
-      <c r="C114" s="14" t="inlineStr"/>
-      <c r="D114" s="14" t="inlineStr">
-        <is>
-          <t>Scott Foster</t>
-        </is>
-      </c>
-      <c r="E114" s="14" t="inlineStr">
+      <c r="C114" s="82" t="inlineStr"/>
+      <c r="D114" s="82" t="inlineStr">
+        <is>
+          <t>Ball State</t>
+        </is>
+      </c>
+      <c r="E114" s="82" t="inlineStr">
         <is>
           <t>Dir. of S&amp;C</t>
         </is>
       </c>
-      <c r="F114" s="15" t="n">
+      <c r="F114" s="83" t="n">
         <v>130000</v>
       </c>
-      <c r="G114" s="14" t="n">
+      <c r="G114" s="82" t="n">
         <v>2024</v>
       </c>
-      <c r="H114" s="16" t="inlineStr">
+      <c r="H114" s="86" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="I114" s="82" t="inlineStr">
+        <is>
+          <t>G5 Mid ($130K-$174K)</t>
+        </is>
+      </c>
+      <c r="J114" s="82" t="n">
+        <v>1</v>
+      </c>
+      <c r="K114" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="82" t="n">
+        <v>1</v>
+      </c>
+      <c r="M114" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" s="82" t="n">
+        <v>2</v>
+      </c>
+      <c r="O114" s="91" t="inlineStr">
         <is>
           <t>Estimated</t>
         </is>
       </c>
-      <c r="I114" s="14" t="inlineStr">
-        <is>
-          <t>G5 Mid ($130K-$174K)</t>
-        </is>
-      </c>
-      <c r="J114" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K114" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M114" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N114" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="O114" s="17" t="inlineStr">
-        <is>
-          <t>Estimated</t>
-        </is>
-      </c>
-      <c r="P114" s="14" t="inlineStr">
+      <c r="P114" s="82" t="inlineStr">
         <is>
           <t>MAC</t>
         </is>
       </c>
-      <c r="Q114" s="14" t="inlineStr"/>
+      <c r="Q114" s="82" t="inlineStr">
+        <is>
+          <t>[Churn 2026-07-17] Name changed: Scott Foster → Ball State. Salary cleared — requires verification.</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="16" customHeight="1">
       <c r="A115" s="82" t="inlineStr">

--- a/data/FBS_SC_Database_v8_1_Clean.xlsx
+++ b/data/FBS_SC_Database_v8_1_Clean.xlsx
@@ -1010,7 +1010,7 @@
       <c r="C4" s="82" t="inlineStr"/>
       <c r="D4" s="82" t="inlineStr">
         <is>
-          <t>South Alabama Football</t>
+          <t>Freddie Roach Added</t>
         </is>
       </c>
       <c r="E4" s="82" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Q4" s="82" t="inlineStr">
         <is>
-          <t>[Churn 2026-07-17] Name changed: David Ballou → South Alabama Football. Salary cleared — requires verification.</t>
+          <t>[Churn 2026-07-17] Name changed: South Alabama Football → Freddie Roach Added. Salary cleared — requires verification.</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       <c r="C10" s="82" t="inlineStr"/>
       <c r="D10" s="85" t="inlineStr">
         <is>
-          <t>Brian Kelly</t>
+          <t>Jake Flint</t>
         </is>
       </c>
       <c r="E10" s="85" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="Q10" s="87" t="inlineStr">
         <is>
-          <t>[Churn 2026-07-17] Name changed: Nick Savage → Brian Kelly. Salary cleared — requires verification.</t>
+          <t>[Churn 2026-07-17] Name changed: Brian Kelly → Jake Flint. Salary cleared — requires verification.</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       <c r="C14" s="82" t="inlineStr"/>
       <c r="D14" s="82" t="inlineStr">
         <is>
-          <t>Jeff Dillman</t>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="E14" s="82" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="Q14" s="82" t="inlineStr">
         <is>
-          <t>[Churn 2026-07-17] Name changed: Luke Day → Jeff Dillman. Salary cleared — requires verification.</t>
+          <t>[Churn 2026-07-17] Name changed: Jeff Dillman → South Carolina. Salary cleared — requires verification.</t>
         </is>
       </c>
     </row>
@@ -2045,7 +2045,7 @@
       <c r="C19" s="82" t="inlineStr"/>
       <c r="D19" s="85" t="inlineStr">
         <is>
-          <t>Colorado State</t>
+          <t>Tyson Brown</t>
         </is>
       </c>
       <c r="E19" s="82" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="Q19" s="85" t="inlineStr">
         <is>
-          <t>[Churn 2026-07-17] Name changed: Unknown → Colorado State. Salary cleared — requires verification.</t>
+          <t>[Churn 2026-07-17] Name changed: Colorado State → Tyson Brown. Salary cleared — requires verification.</t>
         </is>
       </c>
     </row>
@@ -2179,7 +2179,7 @@
       <c r="C21" s="82" t="inlineStr"/>
       <c r="D21" s="82" t="inlineStr">
         <is>
-          <t>Adam Rittenberg</t>
+          <t>Colorado State</t>
         </is>
       </c>
       <c r="E21" s="82" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="Q21" s="82" t="inlineStr">
         <is>
-          <t>[Churn 2026-07-17] Name changed: Ryan Davis → Adam Rittenberg. Salary cleared — requires verification.</t>
+          <t>[Churn 2026-07-17] Name changed: Adam Rittenberg → Colorado State. Salary cleared — requires verification.</t>
         </is>
       </c>
     </row>
@@ -2317,7 +2317,7 @@
       <c r="C23" s="82" t="inlineStr"/>
       <c r="D23" s="82" t="inlineStr">
         <is>
-          <t>Shaquille Lee</t>
+          <t>Michigan State</t>
         </is>
       </c>
       <c r="E23" s="82" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="Q23" s="82" t="inlineStr">
         <is>
-          <t>[Churn 2026-07-17] Name changed: Mike McDonald → Shaquille Lee. Salary cleared — requires verification.</t>
+          <t>[Churn 2026-07-17] Name changed: Shaquille Lee → Michigan State. Salary cleared — requires verification.</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="D32" s="82" t="inlineStr">
         <is>
-          <t>Southern University</t>
+          <t>Cougars Director</t>
         </is>
       </c>
       <c r="E32" s="82" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="Q32" s="82" t="inlineStr">
         <is>
-          <t>[Churn 2026-07-17] Name changed: Aaron Ausmus → Southern University. Salary cleared — requires verification.</t>
+          <t>[Churn 2026-07-17] Name changed: Southern University → Cougars Director. Salary cleared — requires verification.</t>
         </is>
       </c>
     </row>
@@ -3007,7 +3007,7 @@
       <c r="C33" s="82" t="inlineStr"/>
       <c r="D33" s="82" t="inlineStr">
         <is>
-          <t>Jedd Fisch</t>
+          <t>Mark Philipp</t>
         </is>
       </c>
       <c r="E33" s="82" t="inlineStr">
@@ -3058,74 +3058,78 @@
       </c>
       <c r="Q33" s="82" t="inlineStr">
         <is>
-          <t>[Churn 2026-07-17] Name changed: Tyler Owens → Jedd Fisch. Salary cleared — requires verification.</t>
+          <t>[Churn 2026-07-17] Name changed: Jedd Fisch → Mark Philipp. Salary cleared — requires verification.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" s="82" t="inlineStr">
         <is>
           <t>Wisconsin</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B34" s="82" t="inlineStr">
         <is>
           <t>Big Ten</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr"/>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>Brady Collins</t>
-        </is>
-      </c>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="C34" s="82" t="inlineStr"/>
+      <c r="D34" s="82" t="inlineStr">
+        <is>
+          <t>Shaun Snee</t>
+        </is>
+      </c>
+      <c r="E34" s="82" t="inlineStr">
         <is>
           <t>Dir. of S&amp;C</t>
         </is>
       </c>
-      <c r="F34" s="10" t="n">
+      <c r="F34" s="83" t="n">
         <v>455000</v>
       </c>
-      <c r="G34" s="9" t="n">
+      <c r="G34" s="82" t="n">
         <v>2024</v>
       </c>
-      <c r="H34" s="19" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="I34" s="9" t="inlineStr">
+      <c r="H34" s="84" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="I34" s="82" t="inlineStr">
         <is>
           <t>Mid ($350K-$499K)</t>
         </is>
       </c>
-      <c r="J34" s="9" t="n">
+      <c r="J34" s="82" t="n">
         <v>3</v>
       </c>
-      <c r="K34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="M34" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="N34" s="9" t="n">
+      <c r="K34" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="82" t="n">
+        <v>2</v>
+      </c>
+      <c r="M34" s="82" t="n">
+        <v>2</v>
+      </c>
+      <c r="N34" s="82" t="n">
         <v>7</v>
       </c>
-      <c r="O34" s="12" t="inlineStr">
+      <c r="O34" s="88" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="P34" s="9" t="inlineStr">
+      <c r="P34" s="82" t="inlineStr">
         <is>
           <t>FootballScoop 2024</t>
         </is>
       </c>
-      <c r="Q34" s="9" t="inlineStr"/>
+      <c r="Q34" s="82" t="inlineStr">
+        <is>
+          <t>[Churn 2026-07-17] Name changed: Brady Collins → Shaun Snee. Salary cleared — requires verification.</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="82" t="inlineStr">
@@ -3843,7 +3847,7 @@
       </c>
       <c r="D45" s="82" t="inlineStr">
         <is>
-          <t>Before Notre Dame</t>
+          <t>Notre Dame</t>
         </is>
       </c>
       <c r="E45" s="82" t="inlineStr">
@@ -3894,7 +3898,7 @@
       </c>
       <c r="Q45" s="82" t="inlineStr">
         <is>
-          <t>[Churn 2026-07-17] Name changed: Sean Sutton → Before Notre Dame. Salary cleared — requires verification.</t>
+          <t>[Churn 2026-07-17] Name changed: Before Notre Dame → Notre Dame. Salary cleared — requires verification.</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3989,7 @@
       </c>
       <c r="D47" s="82" t="inlineStr">
         <is>
-          <t>Mercer University</t>
+          <t>School Sports Team</t>
         </is>
       </c>
       <c r="E47" s="82" t="inlineStr">
@@ -4036,7 +4040,7 @@
       </c>
       <c r="Q47" s="82" t="inlineStr">
         <is>
-          <t>[Churn 2026-07-17] Name changed: Patrick Redd → Mercer University. Salary cleared — requires verification.</t>
+          <t>[Churn 2026-07-17] Name changed: Mercer University → School Sports Team. Salary cleared — requires verification.</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4200,7 @@
       <c r="C50" s="82" t="inlineStr"/>
       <c r="D50" s="82" t="inlineStr">
         <is>
-          <t>Will Harrison</t>
+          <t>New Virginia</t>
         </is>
       </c>
       <c r="E50" s="82" t="inlineStr">
@@ -4247,7 +4251,7 @@
       </c>
       <c r="Q50" s="82" t="inlineStr">
         <is>
-          <t>[Churn 2026-07-17] Name changed: Adam Smotherman → Will Harrison. Salary cleared — requires verification.</t>
+          <t>[Churn 2026-07-17] Name changed: Will Harrison → New Virginia. Salary cleared — requires verification.</t>
         </is>
       </c>
     </row>
@@ -4265,7 +4269,7 @@
       <c r="C51" s="82" t="inlineStr"/>
       <c r="D51" s="85" t="inlineStr">
         <is>
-          <t>Joined Virginia Tech</t>
+          <t>The Hill</t>
         </is>
       </c>
       <c r="E51" s="85" t="inlineStr">
@@ -4316,7 +4320,7 @@
       </c>
       <c r="Q51" s="87" t="inlineStr">
         <is>
-          <t>[Churn 2026-07-17] Name changed: Chuck Losey → Joined Virginia Tech. Salary cleared — requires verification.</t>
+          <t>[Churn 2026-07-17] Name changed: Joined Virginia Tech → The Hill. Salary cleared — requires verification.</t>
         </is>
       </c>
     </row>
@@ -4756,7 +4760,7 @@
       <c r="C58" s="82" t="inlineStr"/>
       <c r="D58" s="82" t="inlineStr">
         <is>
-          <t>Arkansas State</t>
+          <t>Maurice Sims</t>
         </is>
       </c>
       <c r="E58" s="82" t="inlineStr">
@@ -4807,7 +4811,7 @@
       </c>
       <c r="Q58" s="82" t="inlineStr">
         <is>
-          <t>[Churn 2026-07-17] Name changed: Austin Chambers → Arkansas State. Salary cleared — requires verification.</t>
+          <t>[Churn 2026-07-17] Name changed: Arkansas State → Maurice Sims. Salary cleared — requires verification.</t>
         </is>
       </c>
     </row>
@@ -4963,7 +4967,7 @@
       <c r="C61" s="82" t="inlineStr"/>
       <c r="D61" s="82" t="inlineStr">
         <is>
-          <t>Kansas Team Health</t>
+          <t>Kansas Football Names</t>
         </is>
       </c>
       <c r="E61" s="82" t="inlineStr">
@@ -5014,7 +5018,7 @@
       </c>
       <c r="Q61" s="82" t="inlineStr">
         <is>
-          <t>[Churn 2026-07-17] Name changed: Matt Gildersleeve → Kansas Team Health. Salary cleared — requires verification.</t>
+          <t>[Churn 2026-07-17] Name changed: Kansas Team Health → Kansas Football Names. Salary cleared — requires verification.</t>
         </is>
       </c>
     </row>
@@ -5088,71 +5092,71 @@
       </c>
     </row>
     <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="A63" s="82" t="inlineStr">
         <is>
           <t>Oklahoma</t>
         </is>
       </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="B63" s="82" t="inlineStr">
         <is>
           <t>Big 12</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr"/>
-      <c r="D63" s="64" t="inlineStr">
-        <is>
-          <t>James Dobson</t>
-        </is>
-      </c>
-      <c r="E63" s="64" t="inlineStr">
+      <c r="C63" s="82" t="inlineStr"/>
+      <c r="D63" s="85" t="inlineStr">
+        <is>
+          <t>Head Coach Bobby</t>
+        </is>
+      </c>
+      <c r="E63" s="85" t="inlineStr">
         <is>
           <t>Director of Sports Enhancement &amp; S&amp;C</t>
         </is>
       </c>
-      <c r="F63" s="67" t="n">
+      <c r="F63" s="89" t="n">
         <v>700000</v>
       </c>
-      <c r="G63" s="4" t="n">
+      <c r="G63" s="82" t="n">
         <v>2024</v>
       </c>
-      <c r="H63" s="6" t="inlineStr">
+      <c r="H63" s="84" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="I63" s="82" t="inlineStr">
+        <is>
+          <t>Top ($700K-$999K)</t>
+        </is>
+      </c>
+      <c r="J63" s="85" t="n">
+        <v>4</v>
+      </c>
+      <c r="K63" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="82" t="n">
+        <v>2</v>
+      </c>
+      <c r="M63" s="82" t="n">
+        <v>2</v>
+      </c>
+      <c r="N63" s="85" t="n">
+        <v>5</v>
+      </c>
+      <c r="O63" s="84" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="I63" s="4" t="inlineStr">
-        <is>
-          <t>Top ($700K-$999K)</t>
-        </is>
-      </c>
-      <c r="J63" s="64" t="n">
-        <v>4</v>
-      </c>
-      <c r="K63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M63" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N63" s="64" t="n">
-        <v>5</v>
-      </c>
-      <c r="O63" s="6" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="P63" s="64" t="inlineStr">
+      <c r="P63" s="85" t="inlineStr">
         <is>
           <t>soonersports.com 2026 roster: Dobson (head $700K) + Manninger (Assoc Dir — new) + Kolok (Asst Dir) + Matias (Asst Dir) + Vasquez (Asst Dir — new). 5 paid S&amp;C staff fully named from live roster.</t>
         </is>
       </c>
-      <c r="Q63" s="64" t="inlineStr">
-        <is>
-          <t>Full 2026 staff confirmed from live roster: 5 named paid S&amp;C (Dobson + 4 assts incl. 2 new names Manninger + Vasquez).</t>
+      <c r="Q63" s="85" t="inlineStr">
+        <is>
+          <t>[Churn 2026-07-17] Name changed: James Dobson → Head Coach Bobby. Salary cleared — requires verification.</t>
         </is>
       </c>
     </row>
@@ -5446,7 +5450,7 @@
       <c r="C68" s="82" t="inlineStr"/>
       <c r="D68" s="82" t="inlineStr">
         <is>
-          <t>Cougars Director</t>
+          <t>Head Strength</t>
         </is>
       </c>
       <c r="E68" s="82" t="inlineStr">
@@ -5497,7 +5501,7 @@
       </c>
       <c r="Q68" s="85" t="inlineStr">
         <is>
-          <t>[Churn 2026-07-17] Name changed: Torre Becton → Cougars Director. Salary cleared — requires verification.</t>
+          <t>[Churn 2026-07-17] Name changed: Cougars Director → Head Strength. Salary cleared — requires verification.</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5657,7 @@
       <c r="C71" s="82" t="inlineStr"/>
       <c r="D71" s="85" t="inlineStr">
         <is>
-          <t>New Utah</t>
+          <t>Baltimore Ravens</t>
         </is>
       </c>
       <c r="E71" s="85" t="inlineStr">
@@ -5704,7 +5708,7 @@
       </c>
       <c r="Q71" s="87" t="inlineStr">
         <is>
-          <t>[Churn 2026-07-17] Name changed: Steve Saunders → New Utah. Salary cleared — requires verification.</t>
+          <t>[Churn 2026-07-17] Name changed: New Utah → Baltimore Ravens. Salary cleared — requires verification.</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5933,7 @@
       <c r="C75" s="82" t="inlineStr"/>
       <c r="D75" s="82" t="inlineStr">
         <is>
-          <t>Tyson Brown</t>
+          <t>Joey Guarascio</t>
         </is>
       </c>
       <c r="E75" s="82" t="inlineStr">
@@ -5980,7 +5984,7 @@
       </c>
       <c r="Q75" s="82" t="inlineStr">
         <is>
-          <t>[Churn 2026-07-17] Name changed: Dave Bailey → Tyson Brown. Salary cleared — requires verification.</t>
+          <t>[Churn 2026-07-17] Name changed: Tyson Brown → Joey Guarascio. Salary cleared — requires verification.</t>
         </is>
       </c>
     </row>
@@ -6822,7 +6826,7 @@
       <c r="C88" s="82" t="inlineStr"/>
       <c r="D88" s="85" t="inlineStr">
         <is>
-          <t>Miami Northwestern Assistant</t>
+          <t>Florida Atlantic Football</t>
         </is>
       </c>
       <c r="E88" s="85" t="inlineStr">
@@ -6873,7 +6877,7 @@
       </c>
       <c r="Q88" s="87" t="inlineStr">
         <is>
-          <t>[Churn 2026-07-17] Name changed: Brandon Lee, CSCS → Miami Northwestern Assistant. Salary cleared — requires verification.</t>
+          <t>[Churn 2026-07-17] Name changed: Miami Northwestern Assistant → Florida Atlantic Football. Salary cleared — requires verification.</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7244,7 @@
       <c r="C94" s="82" t="inlineStr"/>
       <c r="D94" s="82" t="inlineStr">
         <is>
-          <t>Temple Football</t>
+          <t>Stephen Whitlock</t>
         </is>
       </c>
       <c r="E94" s="82" t="inlineStr">
@@ -7291,7 +7295,7 @@
       </c>
       <c r="Q94" s="82" t="inlineStr">
         <is>
-          <t>[Churn 2026-07-17] Name changed: Brad Traynor → Temple Football. Salary cleared — requires verification.</t>
+          <t>[Churn 2026-07-17] Name changed: Temple Football → Stephen Whitlock. Salary cleared — requires verification.</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7317,7 @@
       </c>
       <c r="D95" s="85" t="inlineStr">
         <is>
-          <t>Kyle Speer</t>
+          <t>Tulane University</t>
         </is>
       </c>
       <c r="E95" s="82" t="inlineStr">
@@ -7364,7 +7368,7 @@
       </c>
       <c r="Q95" s="85" t="inlineStr">
         <is>
-          <t>[Churn 2026-07-17] Name changed: Unknown → Kyle Speer. Salary cleared — requires verification.</t>
+          <t>[Churn 2026-07-17] Name changed: Kyle Speer → Tulane University. Salary cleared — requires verification.</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7662,7 @@
       <c r="C100" s="82" t="inlineStr"/>
       <c r="D100" s="82" t="inlineStr">
         <is>
-          <t>Central Arkansas</t>
+          <t>Ben Herbert</t>
         </is>
       </c>
       <c r="E100" s="82" t="inlineStr">
@@ -7709,7 +7713,7 @@
       </c>
       <c r="Q100" s="82" t="inlineStr">
         <is>
-          <t>[Churn 2026-07-17] Name changed: Jake Ross → Central Arkansas. Salary cleared — requires verification.</t>
+          <t>[Churn 2026-07-17] Name changed: Central Arkansas → Ben Herbert. Salary cleared — requires verification.</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8145,7 @@
       <c r="C107" s="82" t="inlineStr"/>
       <c r="D107" s="82" t="inlineStr">
         <is>
-          <t>Marshall Football Family</t>
+          <t>Dwight Galt</t>
         </is>
       </c>
       <c r="E107" s="82" t="inlineStr">
@@ -8192,7 +8196,7 @@
       </c>
       <c r="Q107" s="82" t="inlineStr">
         <is>
-          <t>[Churn 2026-07-17] Name changed: Cam Shelmadine → Marshall Football Family. Salary cleared — requires verification.</t>
+          <t>[Churn 2026-07-17] Name changed: Marshall Football Family → Dwight Galt. Salary cleared — requires verification.</t>
         </is>
       </c>
     </row>
@@ -8279,7 +8283,7 @@
       <c r="C109" s="82" t="inlineStr"/>
       <c r="D109" s="82" t="inlineStr">
         <is>
-          <t>South Alabama Football</t>
+          <t>Matt Shadeed</t>
         </is>
       </c>
       <c r="E109" s="82" t="inlineStr">
@@ -8330,7 +8334,7 @@
       </c>
       <c r="Q109" s="82" t="inlineStr">
         <is>
-          <t>[Churn 2026-07-17] Name changed: Marcus Edgerton → South Alabama Football. Salary cleared — requires verification.</t>
+          <t>[Churn 2026-07-17] Name changed: South Alabama Football → Matt Shadeed. Salary cleared — requires verification.</t>
         </is>
       </c>
     </row>
@@ -8473,71 +8477,71 @@
       </c>
     </row>
     <row r="112" ht="16" customHeight="1">
-      <c r="A112" s="14" t="inlineStr">
+      <c r="A112" s="82" t="inlineStr">
         <is>
           <t>Troy</t>
         </is>
       </c>
-      <c r="B112" s="14" t="inlineStr">
+      <c r="B112" s="82" t="inlineStr">
         <is>
           <t>Sun Belt</t>
         </is>
       </c>
-      <c r="C112" s="14" t="inlineStr"/>
-      <c r="D112" s="71" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E112" s="14" t="inlineStr">
+      <c r="C112" s="82" t="inlineStr"/>
+      <c r="D112" s="85" t="inlineStr">
+        <is>
+          <t>Darl Bauer</t>
+        </is>
+      </c>
+      <c r="E112" s="82" t="inlineStr">
         <is>
           <t>Dir. of S&amp;C</t>
         </is>
       </c>
-      <c r="F112" s="15" t="n">
+      <c r="F112" s="83" t="n">
         <v>150000</v>
       </c>
-      <c r="G112" s="14" t="n">
+      <c r="G112" s="82" t="n">
         <v>2026</v>
       </c>
-      <c r="H112" s="16" t="inlineStr">
+      <c r="H112" s="86" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="I112" s="82" t="inlineStr">
+        <is>
+          <t>G5 Mid ($130K-$174K)</t>
+        </is>
+      </c>
+      <c r="J112" s="82" t="n">
+        <v>1</v>
+      </c>
+      <c r="K112" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" s="82" t="n">
+        <v>1</v>
+      </c>
+      <c r="M112" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" s="82" t="n">
+        <v>2</v>
+      </c>
+      <c r="O112" s="91" t="inlineStr">
         <is>
           <t>Estimated</t>
         </is>
       </c>
-      <c r="I112" s="14" t="inlineStr">
-        <is>
-          <t>G5 Mid ($130K-$174K)</t>
-        </is>
-      </c>
-      <c r="J112" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K112" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L112" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M112" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N112" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="O112" s="17" t="inlineStr">
-        <is>
-          <t>Estimated</t>
-        </is>
-      </c>
-      <c r="P112" s="14" t="inlineStr">
+      <c r="P112" s="82" t="inlineStr">
         <is>
           <t>Whitt followed Sumrall to Florida. Troy has new HC after Sumrall left.</t>
         </is>
       </c>
-      <c r="Q112" s="71" t="inlineStr">
-        <is>
-          <t>Sumrall/Whitt chain; Troy has new HC; S&amp;C status not confirmed.</t>
+      <c r="Q112" s="85" t="inlineStr">
+        <is>
+          <t>[Churn 2026-07-17] Name changed: Unknown → Darl Bauer. Salary cleared — requires verification.</t>
         </is>
       </c>
     </row>
@@ -8555,7 +8559,7 @@
       <c r="C113" s="82" t="inlineStr"/>
       <c r="D113" s="82" t="inlineStr">
         <is>
-          <t>Youngstown State</t>
+          <t>Follow Akron Football</t>
         </is>
       </c>
       <c r="E113" s="82" t="inlineStr">
@@ -8606,7 +8610,7 @@
       </c>
       <c r="Q113" s="82" t="inlineStr">
         <is>
-          <t>[Churn 2026-07-17] Name changed: Drew Hankinson → Youngstown State. Salary cleared — requires verification.</t>
+          <t>[Churn 2026-07-17] Name changed: Youngstown State → Follow Akron Football. Salary cleared — requires verification.</t>
         </is>
       </c>
     </row>
@@ -9431,71 +9435,71 @@
       </c>
     </row>
     <row r="126" ht="16" customHeight="1">
-      <c r="A126" s="14" t="inlineStr">
+      <c r="A126" s="82" t="inlineStr">
         <is>
           <t>Florida Intl</t>
         </is>
       </c>
-      <c r="B126" s="14" t="inlineStr">
+      <c r="B126" s="82" t="inlineStr">
         <is>
           <t>CUSA</t>
         </is>
       </c>
-      <c r="C126" s="14" t="inlineStr"/>
-      <c r="D126" s="71" t="inlineStr">
-        <is>
-          <t>Matt Hickmann</t>
-        </is>
-      </c>
-      <c r="E126" s="71" t="inlineStr">
+      <c r="C126" s="82" t="inlineStr"/>
+      <c r="D126" s="85" t="inlineStr">
+        <is>
+          <t>Ryan Horton</t>
+        </is>
+      </c>
+      <c r="E126" s="85" t="inlineStr">
         <is>
           <t>Director of S&amp;C</t>
         </is>
       </c>
-      <c r="F126" s="72" t="n">
+      <c r="F126" s="89" t="n">
         <v>140000</v>
       </c>
-      <c r="G126" s="14" t="n">
+      <c r="G126" s="82" t="n">
         <v>2024</v>
       </c>
-      <c r="H126" s="16" t="inlineStr">
-        <is>
-          <t>Confirmed (name)</t>
-        </is>
-      </c>
-      <c r="I126" s="14" t="inlineStr">
+      <c r="H126" s="86" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="I126" s="82" t="inlineStr">
         <is>
           <t>G5 Mid ($130K-$174K)</t>
         </is>
       </c>
-      <c r="J126" s="71" t="n">
-        <v>1</v>
-      </c>
-      <c r="K126" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M126" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N126" s="71" t="n">
-        <v>2</v>
-      </c>
-      <c r="O126" s="16" t="inlineStr">
+      <c r="J126" s="85" t="n">
+        <v>1</v>
+      </c>
+      <c r="K126" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="82" t="n">
+        <v>1</v>
+      </c>
+      <c r="M126" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" s="85" t="n">
+        <v>2</v>
+      </c>
+      <c r="O126" s="86" t="inlineStr">
         <is>
           <t>Confirmed (name); Estimated (salary)</t>
         </is>
       </c>
-      <c r="P126" s="71" t="inlineStr">
+      <c r="P126" s="85" t="inlineStr">
         <is>
           <t>fiusports.com 2026 live football roster: Hickmann (Dir S&amp;C, in first year; 6 yrs MTSU + GA Tech 2012-14 + Furman + Cumberland) + Anthony Rahar (Asst S&amp;C). Also: Madison Buckley (Head Sports Nutritionist). HC Willie Simmons hired Dec 7 2024 (from Duke/FAMU). Gage Parker was INCORRECT.</t>
         </is>
       </c>
-      <c r="Q126" s="18" t="inlineStr">
-        <is>
-          <t>MAJOR: Gage Parker incorrect. Hickmann confirmed Dir S&amp;C per live 2026 FIU roster. HC Simmons Dec 2024.</t>
+      <c r="Q126" s="87" t="inlineStr">
+        <is>
+          <t>[Churn 2026-07-17] Name changed: Matt Hickmann → Ryan Horton. Salary cleared — requires verification.</t>
         </is>
       </c>
     </row>
